--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487612_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487612_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1902</v>
+        <v>6.2169</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9111</v>
+        <v>1.415</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2791</v>
+        <v>4.802</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9198</v>
+        <v>4.8698</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0015</v>
+        <v>2.671</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08169999999999999</v>
+        <v>2.1989</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5644</v>
+        <v>3.1598</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9752</v>
+        <v>2.5458</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.4108</v>
+        <v>0.614</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3554</v>
+        <v>1.7101</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0263</v>
+        <v>0.1252</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3291</v>
+        <v>1.5849</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.5224</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2869</v>
+        <v>1.6277</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2454</v>
+        <v>0.2717</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0415</v>
+        <v>1.356</v>
       </c>
       <c r="V2" t="n">
-        <v>1.506</v>
+        <v>1.2716</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0119</v>
+        <v>0.894</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.506</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1078</v>
+        <v>5.1347</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5448</v>
+        <v>3.9102</v>
       </c>
       <c r="F3" t="n">
-        <v>3.563</v>
+        <v>1.2246</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9853</v>
+        <v>3.9198</v>
       </c>
       <c r="H3" t="n">
-        <v>2.297</v>
+        <v>4.0015</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6884</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1972</v>
+        <v>2.5644</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2327</v>
+        <v>3.9752</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0356</v>
+        <v>-1.4108</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7882</v>
+        <v>1.3554</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0263</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7239</v>
+        <v>1.3291</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1702</v>
+        <v>2.2314</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3656</v>
+        <v>1.2444</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8046</v>
+        <v>0.987</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0478</v>
+        <v>3.0119</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5886</v>
+        <v>5.0984</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1137</v>
+        <v>1.3446</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4749</v>
+        <v>3.7537</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8698</v>
+        <v>3.9853</v>
       </c>
       <c r="H4" t="n">
-        <v>2.671</v>
+        <v>2.297</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1989</v>
+        <v>1.6884</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1598</v>
+        <v>2.1972</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5458</v>
+        <v>2.2327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.614</v>
+        <v>-0.0356</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7101</v>
+        <v>1.7882</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1252</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5849</v>
+        <v>1.7239</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5523</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0007</v>
+        <v>1.1608</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0296</v>
+        <v>0.1654</v>
       </c>
       <c r="U4" t="n">
-        <v>1.029</v>
+        <v>0.9954</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2716</v>
+        <v>-0.0478</v>
       </c>
       <c r="W4" t="n">
-        <v>0.894</v>
+        <v>-0.0478</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7114</v>
+        <v>2.9017</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3371</v>
+        <v>0.6364</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3743</v>
+        <v>2.2653</v>
       </c>
       <c r="G5" t="n">
         <v>2.3676</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2557</v>
+        <v>1.446</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2146</v>
+        <v>0.5139</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0411</v>
+        <v>0.9321</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3299</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0388</v>
+        <v>-0.2615</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7092</v>
+        <v>-2.0095</v>
       </c>
       <c r="F6" t="n">
         <v>1.748</v>
@@ -922,10 +922,10 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4558</v>
+        <v>1.1555</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8501</v>
+        <v>0.5498</v>
       </c>
       <c r="U6" t="n">
         <v>0.6057</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5148</v>
+        <v>-0.9685</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.0061</v>
+        <v>-0.9506</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4913</v>
+        <v>-0.0179</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8074</v>
+        <v>0.1685</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9526</v>
+        <v>0.2669</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1451</v>
+        <v>-0.0984</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.7948</v>
+        <v>0.0406</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4829</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3118</v>
+        <v>0.0406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.1279</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4696</v>
+        <v>0.2669</v>
       </c>
       <c r="O7" t="n">
-        <v>1.457</v>
+        <v>-0.139</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1867</v>
+        <v>0.1152</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2412</v>
+        <v>-0.021</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4278</v>
+        <v>0.1363</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1504</v>
+        <v>-1.3183</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0507</v>
+        <v>-3.2996</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0997</v>
+        <v>1.9813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1685</v>
+        <v>1.2858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2669</v>
+        <v>-0.7629</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0984</v>
+        <v>2.0487</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0406</v>
+        <v>0.5825</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.1483</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>0.7307</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1279</v>
+        <v>0.7033</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2669</v>
+        <v>-0.6146</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.139</v>
+        <v>1.3179</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.9183</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1211</v>
+        <v>-0.0014</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0545</v>
+        <v>0.9197</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9457</v>
+        <v>-1.4231</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5999</v>
+        <v>-3.906</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6542</v>
+        <v>2.4829</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2858</v>
+        <v>-1.8074</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7629</v>
+        <v>-1.9526</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0487</v>
+        <v>0.1451</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5825</v>
+        <v>-2.7948</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1483</v>
+        <v>-1.4829</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7307</v>
+        <v>-1.3118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7033</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6146</v>
+        <v>-0.4696</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3179</v>
+        <v>1.457</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2909</v>
+        <v>1.2783</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3017</v>
+        <v>-0.1411</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5927</v>
+        <v>1.4194</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0752</v>
+        <v>-1.4295</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5759</v>
+        <v>-3.1755</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5008</v>
+        <v>1.746</v>
       </c>
       <c r="G10" t="n">
         <v>1.0494</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9397</v>
+        <v>1.5853</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3039</v>
+        <v>0.7043</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6357</v>
+        <v>0.881</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3776</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.9507</v>
+        <v>13.9508</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0351</v>
+        <v>-6.035</v>
       </c>
       <c r="F11" t="n">
         <v>19.9859</v>
@@ -1282,7 +1282,7 @@
         <v>11.1552</v>
       </c>
       <c r="I11" t="n">
-        <v>4.004000000000001</v>
+        <v>4.004</v>
       </c>
       <c r="J11" t="n">
         <v>6.0569</v>
@@ -1291,7 +1291,7 @@
         <v>12.6466</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.589799999999999</v>
+        <v>-6.5898</v>
       </c>
       <c r="M11" t="n">
         <v>9.102399999999999</v>
@@ -1312,7 +1312,7 @@
         <v>6.7912</v>
       </c>
       <c r="S11" t="n">
-        <v>11.5186</v>
+        <v>11.5185</v>
       </c>
       <c r="T11" t="n">
         <v>3.286</v>
@@ -1324,7 +1324,7 @@
         <v>-1.0851</v>
       </c>
       <c r="W11" t="n">
-        <v>3.055099999999999</v>
+        <v>3.0551</v>
       </c>
       <c r="X11" t="n">
         <v>-4.1403</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1772</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9996</v>
+        <v>0.5637</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1777</v>
+        <v>0.3521</v>
       </c>
       <c r="G12" t="n">
-        <v>2.056</v>
+        <v>-1.278</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5983</v>
+        <v>-1.7079</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4577</v>
+        <v>0.4299</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7858</v>
+        <v>0.1107</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1966</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4108</v>
+        <v>-0.6267</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2702</v>
+        <v>-1.3887</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5983</v>
+        <v>-2.4453</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8685</v>
+        <v>1.0566</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9403</v>
+        <v>2.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5687</v>
+        <v>-2.2704</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1839</v>
+        <v>-1.335</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7526</v>
+        <v>-0.9354</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2803</v>
+        <v>1.5537</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2803</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4033</v>
+        <v>0.649</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0194</v>
+        <v>0.1988</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4227</v>
+        <v>0.4502</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4416</v>
+        <v>2.056</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1747</v>
+        <v>1.5983</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2669</v>
+        <v>0.4577</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0412</v>
+        <v>1.7858</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0412</v>
+        <v>3.1966</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.4108</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4004</v>
+        <v>0.2702</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1335</v>
+        <v>-1.5983</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2669</v>
+        <v>1.8685</v>
       </c>
       <c r="P13" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R13" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1759</v>
+        <v>-1.0969</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0606</v>
+        <v>-0.6169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1153</v>
+        <v>-0.48</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0564</v>
+        <v>-1.2803</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0564</v>
+        <v>-1.2803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3975</v>
+        <v>0.4306</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2634</v>
+        <v>-0.0194</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1341</v>
+        <v>0.45</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.278</v>
+        <v>0.4416</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7079</v>
+        <v>0.1747</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4299</v>
+        <v>0.2669</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1107</v>
+        <v>0.0412</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.0412</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6267</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3887</v>
+        <v>0.4004</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4453</v>
+        <v>0.1335</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0566</v>
+        <v>0.2669</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9105</v>
+        <v>0.194</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9105</v>
+        <v>0.194</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7887</v>
+        <v>-0.1486</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6353</v>
+        <v>-0.0606</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1534</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5537</v>
+        <v>-0.0564</v>
       </c>
       <c r="W14" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2343</v>
+        <v>-0.0564</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.768</v>
+        <v>-0.9226</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8076</v>
+        <v>-1.9077</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0396</v>
+        <v>0.9851</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2223</v>
@@ -1624,13 +1624,13 @@
         <v>3.4926</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.758</v>
+        <v>-1.9126</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3314</v>
+        <v>-1.4315</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4266</v>
+        <v>-0.4811</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2803</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1268</v>
+        <v>-1.2358</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0606</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0662</v>
+        <v>-1.1752</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0725</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1696</v>
+        <v>0.0606</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2302</v>
+        <v>0.1211</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5101</v>
+        <v>-1.4829</v>
       </c>
       <c r="E17" t="n">
         <v>-1.5164</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0062</v>
+        <v>0.0335</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2737</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4305</v>
+        <v>-0.4032</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.867</v>
+        <v>-1.813</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5613</v>
+        <v>-2.8616</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6942</v>
+        <v>1.0486</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3063</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9998</v>
+        <v>-0.9458</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3017</v>
+        <v>-0.602</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.3437</v>
       </c>
       <c r="V18" t="n">
         <v>0.6032999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9955</v>
+        <v>-2.4521</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.0719</v>
+        <v>-3.6597</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0764</v>
+        <v>1.2076</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.9184</v>
+        <v>-4.4484</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.7817</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1367</v>
+        <v>-3.7654</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.7302</v>
+        <v>-2.4363</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.8094</v>
+        <v>2.1132</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9208</v>
+        <v>-4.5495</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1883</v>
+        <v>-2.0122</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9724</v>
+        <v>-2.7962</v>
       </c>
       <c r="O19" t="n">
         <v>0.7841</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3284</v>
+        <v>2.1344</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2985</v>
+        <v>3.1045</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5711</v>
+        <v>-2.0216</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.8776</v>
+        <v>-1.4772</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3065</v>
+        <v>-0.5445</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1657</v>
+        <v>1.8836</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
         <v>0.6597</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0433</v>
+        <v>-3.1129</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0601</v>
+        <v>-5.6715</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0168</v>
+        <v>2.5586</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.4484</v>
+        <v>-5.9184</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-4.7817</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.7654</v>
+        <v>-1.1367</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4363</v>
+        <v>-4.7302</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1132</v>
+        <v>-2.8094</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.5495</v>
+        <v>-1.9208</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0122</v>
+        <v>-1.1883</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.7962</v>
+        <v>-1.9724</v>
       </c>
       <c r="O20" t="n">
         <v>0.7841</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1344</v>
+        <v>2.3284</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1045</v>
+        <v>3.2985</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6128</v>
+        <v>-1.6885</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8776</v>
+        <v>-1.4772</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7353</v>
+        <v>-0.2114</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8836</v>
+        <v>2.1657</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
         <v>0.6597</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6181</v>
+        <v>-4.9268</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1516</v>
+        <v>-5.0515</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5336</v>
+        <v>0.1247</v>
       </c>
       <c r="G21" t="n">
         <v>-3.137</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-1.0916</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0902</v>
+        <v>-0.9901</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3073</v>
+        <v>-0.1015</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2803</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.9508</v>
+        <v>-13.9507</v>
       </c>
       <c r="E22" t="n">
         <v>-19.9859</v>
       </c>
       <c r="F22" t="n">
-        <v>6.0351</v>
+        <v>6.0352</v>
       </c>
       <c r="G22" t="n">
         <v>-15.159</v>
@@ -2152,7 +2152,7 @@
         <v>-10.5936</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.056900000000001</v>
+        <v>-6.0569</v>
       </c>
       <c r="N22" t="n">
         <v>-12.6465</v>
@@ -2170,13 +2170,13 @@
         <v>18.433</v>
       </c>
       <c r="S22" t="n">
-        <v>-11.5187</v>
+        <v>-11.5186</v>
       </c>
       <c r="T22" t="n">
         <v>-8.232800000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.2861</v>
+        <v>-3.286</v>
       </c>
       <c r="V22" t="n">
         <v>1.0851</v>
